--- a/artfynd/A 3222-2026 artfynd.xlsx
+++ b/artfynd/A 3222-2026 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131092646</v>
+        <v>131085805</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,13 +1270,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585082</v>
+        <v>585215</v>
       </c>
       <c r="R7" t="n">
-        <v>7060264</v>
+        <v>7060513</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,9 +1303,19 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,22 +1330,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131086958</v>
+        <v>131092646</v>
       </c>
       <c r="B8" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,13 +1377,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585165</v>
+        <v>585082</v>
       </c>
       <c r="R8" t="n">
-        <v>7060565</v>
+        <v>7060264</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1400,19 +1410,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,22 +1427,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131085613</v>
+        <v>131086958</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,42 +1450,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585222</v>
+        <v>585165</v>
       </c>
       <c r="R9" t="n">
-        <v>7060481</v>
+        <v>7060565</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1514,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1524,12 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:52</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack gran</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,22 +1534,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131085805</v>
+        <v>131085613</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,37 +1557,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585215</v>
+        <v>585222</v>
       </c>
       <c r="R10" t="n">
-        <v>7060513</v>
+        <v>7060481</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1626,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1636,7 +1631,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,22 +1651,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131087481</v>
+        <v>131085696</v>
       </c>
       <c r="B11" t="n">
-        <v>91833</v>
+        <v>57884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,33 +1674,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585150</v>
+        <v>585207</v>
       </c>
       <c r="R11" t="n">
-        <v>7060657</v>
+        <v>7060471</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1727,9 +1736,24 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1744,22 +1768,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131085696</v>
+        <v>131087481</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>91834</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1767,42 +1791,33 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585207</v>
+        <v>585150</v>
       </c>
       <c r="R12" t="n">
-        <v>7060471</v>
+        <v>7060657</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1829,24 +1844,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,12 +1861,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1876,7 +1876,7 @@
         <v>131085209</v>
       </c>
       <c r="B13" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>131085114</v>
       </c>
       <c r="B14" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>131085107</v>
       </c>
       <c r="B16" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>131092560</v>
       </c>
       <c r="B18" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131085737</v>
+        <v>131092554</v>
       </c>
       <c r="B19" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2504,34 +2504,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585170</v>
+        <v>585147</v>
       </c>
       <c r="R19" t="n">
-        <v>7060469</v>
+        <v>7060312</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2561,19 +2566,14 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:58</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2600,10 +2600,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131085446</v>
+        <v>131086957</v>
       </c>
       <c r="B20" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2611,34 +2611,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585301</v>
+        <v>585162</v>
       </c>
       <c r="R20" t="n">
-        <v>7060488</v>
+        <v>7060573</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2670,7 +2675,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2680,7 +2685,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2707,10 +2717,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131092554</v>
+        <v>131085737</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2718,39 +2728,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585147</v>
+        <v>585170</v>
       </c>
       <c r="R21" t="n">
-        <v>7060312</v>
+        <v>7060469</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2780,14 +2785,19 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2814,10 +2824,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131086957</v>
+        <v>131085446</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,39 +2835,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585162</v>
+        <v>585301</v>
       </c>
       <c r="R22" t="n">
-        <v>7060573</v>
+        <v>7060488</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2889,7 +2894,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2899,12 +2904,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2934,7 +2934,7 @@
         <v>131085201</v>
       </c>
       <c r="B23" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>131085180</v>
       </c>
       <c r="B25" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131085171</v>
+        <v>131085178</v>
       </c>
       <c r="B28" t="n">
-        <v>91809</v>
+        <v>91834</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3477,23 +3477,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3501,13 +3497,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585222</v>
+        <v>585225</v>
       </c>
       <c r="R28" t="n">
-        <v>7060254</v>
+        <v>7060258</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3534,9 +3530,19 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3551,22 +3557,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131085178</v>
+        <v>131085171</v>
       </c>
       <c r="B29" t="n">
-        <v>91833</v>
+        <v>91810</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3574,19 +3580,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3594,13 +3604,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585225</v>
+        <v>585222</v>
       </c>
       <c r="R29" t="n">
-        <v>7060258</v>
+        <v>7060254</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3627,19 +3637,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3654,12 +3654,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3890,10 +3890,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131092585</v>
+        <v>131085569</v>
       </c>
       <c r="B32" t="n">
-        <v>91809</v>
+        <v>79246</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3901,21 +3901,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585130</v>
+        <v>585249</v>
       </c>
       <c r="R32" t="n">
-        <v>7060263</v>
+        <v>7060505</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3987,10 +3987,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131085569</v>
+        <v>131087388</v>
       </c>
       <c r="B33" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>585249</v>
+        <v>585131</v>
       </c>
       <c r="R33" t="n">
-        <v>7060505</v>
+        <v>7060627</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4084,10 +4084,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131087388</v>
+        <v>131092590</v>
       </c>
       <c r="B34" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4119,13 +4119,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>585131</v>
+        <v>585145</v>
       </c>
       <c r="R34" t="n">
-        <v>7060627</v>
+        <v>7060230</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4152,9 +4152,19 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4169,22 +4179,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131092590</v>
+        <v>131092585</v>
       </c>
       <c r="B35" t="n">
-        <v>79245</v>
+        <v>91810</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4192,21 +4202,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4216,13 +4226,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>585145</v>
+        <v>585130</v>
       </c>
       <c r="R35" t="n">
-        <v>7060230</v>
+        <v>7060263</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4249,19 +4259,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4276,12 +4276,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>

--- a/artfynd/A 3222-2026 artfynd.xlsx
+++ b/artfynd/A 3222-2026 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131085805</v>
+        <v>131085613</v>
       </c>
       <c r="B7" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,37 +1246,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585215</v>
+        <v>585222</v>
       </c>
       <c r="R7" t="n">
-        <v>7060513</v>
+        <v>7060481</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1320,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,22 +1340,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131092646</v>
+        <v>131085805</v>
       </c>
       <c r="B8" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,13 +1387,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585082</v>
+        <v>585215</v>
       </c>
       <c r="R8" t="n">
-        <v>7060264</v>
+        <v>7060513</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1410,9 +1420,19 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,22 +1447,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131086958</v>
+        <v>131092646</v>
       </c>
       <c r="B9" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,13 +1494,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585165</v>
+        <v>585082</v>
       </c>
       <c r="R9" t="n">
-        <v>7060565</v>
+        <v>7060264</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1507,19 +1527,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,22 +1544,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131085613</v>
+        <v>131086958</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,42 +1567,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585222</v>
+        <v>585165</v>
       </c>
       <c r="R10" t="n">
-        <v>7060481</v>
+        <v>7060565</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1621,7 +1626,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1631,12 +1636,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:52</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack gran</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,22 +1651,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131085696</v>
+        <v>131087481</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>91836</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,42 +1674,33 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585207</v>
+        <v>585150</v>
       </c>
       <c r="R11" t="n">
-        <v>7060471</v>
+        <v>7060657</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1736,24 +1727,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,22 +1744,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131087481</v>
+        <v>131085696</v>
       </c>
       <c r="B12" t="n">
-        <v>91834</v>
+        <v>57886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,33 +1767,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585150</v>
+        <v>585207</v>
       </c>
       <c r="R12" t="n">
-        <v>7060657</v>
+        <v>7060471</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1844,9 +1829,24 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,12 +1861,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1876,7 +1876,7 @@
         <v>131085209</v>
       </c>
       <c r="B13" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>131085114</v>
       </c>
       <c r="B14" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>131089847</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131085107</v>
+        <v>131092632</v>
       </c>
       <c r="B16" t="n">
-        <v>91834</v>
+        <v>57886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2197,30 +2197,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585194</v>
+        <v>585099</v>
       </c>
       <c r="R16" t="n">
-        <v>7060227</v>
+        <v>7060260</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2253,6 +2262,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2279,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131092632</v>
+        <v>131085107</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>91836</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,39 +2304,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585099</v>
+        <v>585194</v>
       </c>
       <c r="R17" t="n">
-        <v>7060260</v>
+        <v>7060227</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2355,11 +2360,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2386,10 +2386,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131092560</v>
+        <v>131092554</v>
       </c>
       <c r="B18" t="n">
-        <v>91810</v>
+        <v>57886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,37 +2397,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585129</v>
+        <v>585147</v>
       </c>
       <c r="R18" t="n">
-        <v>7060254</v>
+        <v>7060312</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2454,19 +2459,14 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:17</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2481,22 +2481,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131092554</v>
+        <v>131086957</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585147</v>
+        <v>585162</v>
       </c>
       <c r="R19" t="n">
-        <v>7060312</v>
+        <v>7060573</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2566,14 +2566,24 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre ringhack, gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2588,22 +2598,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131086957</v>
+        <v>131085737</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2611,42 +2621,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585162</v>
+        <v>585170</v>
       </c>
       <c r="R20" t="n">
-        <v>7060573</v>
+        <v>7060469</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2675,7 +2680,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2685,12 +2690,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2705,22 +2705,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131085737</v>
+        <v>131085446</v>
       </c>
       <c r="B21" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2752,13 +2752,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585170</v>
+        <v>585301</v>
       </c>
       <c r="R21" t="n">
-        <v>7060469</v>
+        <v>7060488</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2812,22 +2812,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131085446</v>
+        <v>131092560</v>
       </c>
       <c r="B22" t="n">
-        <v>79246</v>
+        <v>91812</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,21 +2835,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585301</v>
+        <v>585129</v>
       </c>
       <c r="R22" t="n">
-        <v>7060488</v>
+        <v>7060254</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2934,7 +2934,7 @@
         <v>131085201</v>
       </c>
       <c r="B23" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>131089835</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>131085180</v>
       </c>
       <c r="B25" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>131087026</v>
       </c>
       <c r="B26" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>131085159</v>
       </c>
       <c r="B27" t="n">
-        <v>56456</v>
+        <v>56458</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131085178</v>
+        <v>131085171</v>
       </c>
       <c r="B28" t="n">
-        <v>91834</v>
+        <v>91812</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3477,19 +3477,23 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3497,13 +3501,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585225</v>
+        <v>585222</v>
       </c>
       <c r="R28" t="n">
-        <v>7060258</v>
+        <v>7060254</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3530,19 +3534,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3557,22 +3551,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131085171</v>
+        <v>131085178</v>
       </c>
       <c r="B29" t="n">
-        <v>91810</v>
+        <v>91836</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3580,23 +3574,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3604,13 +3594,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585222</v>
+        <v>585225</v>
       </c>
       <c r="R29" t="n">
-        <v>7060254</v>
+        <v>7060258</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3637,9 +3627,19 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3654,12 +3654,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3669,7 +3669,7 @@
         <v>131085484</v>
       </c>
       <c r="B30" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>131085240</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3890,10 +3890,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131085569</v>
+        <v>131085126</v>
       </c>
       <c r="B32" t="n">
-        <v>79246</v>
+        <v>57066</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3901,34 +3901,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585249</v>
+        <v>585219</v>
       </c>
       <c r="R32" t="n">
-        <v>7060505</v>
+        <v>7060240</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3987,10 +3992,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131087388</v>
+        <v>131085569</v>
       </c>
       <c r="B33" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4022,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>585131</v>
+        <v>585249</v>
       </c>
       <c r="R33" t="n">
-        <v>7060627</v>
+        <v>7060505</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4084,10 +4089,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131092590</v>
+        <v>131087388</v>
       </c>
       <c r="B34" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4119,13 +4124,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>585145</v>
+        <v>585131</v>
       </c>
       <c r="R34" t="n">
-        <v>7060230</v>
+        <v>7060627</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4152,19 +4157,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4179,22 +4174,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131092585</v>
+        <v>131092590</v>
       </c>
       <c r="B35" t="n">
-        <v>91810</v>
+        <v>79248</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4202,21 +4197,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4226,13 +4221,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>585130</v>
+        <v>585145</v>
       </c>
       <c r="R35" t="n">
-        <v>7060263</v>
+        <v>7060230</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4259,9 +4254,19 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4276,22 +4281,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131085126</v>
+        <v>131092585</v>
       </c>
       <c r="B36" t="n">
-        <v>57064</v>
+        <v>91812</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4299,39 +4304,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>585219</v>
+        <v>585130</v>
       </c>
       <c r="R36" t="n">
-        <v>7060240</v>
+        <v>7060263</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>

--- a/artfynd/A 3222-2026 artfynd.xlsx
+++ b/artfynd/A 3222-2026 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131085613</v>
+        <v>131085805</v>
       </c>
       <c r="B7" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,42 +1246,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585222</v>
+        <v>585215</v>
       </c>
       <c r="R7" t="n">
-        <v>7060481</v>
+        <v>7060513</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,12 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:52</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack gran</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,22 +1330,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131085805</v>
+        <v>131092646</v>
       </c>
       <c r="B8" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,13 +1377,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585215</v>
+        <v>585082</v>
       </c>
       <c r="R8" t="n">
-        <v>7060513</v>
+        <v>7060264</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,19 +1410,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,22 +1427,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131092646</v>
+        <v>131086958</v>
       </c>
       <c r="B9" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,13 +1474,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585082</v>
+        <v>585165</v>
       </c>
       <c r="R9" t="n">
-        <v>7060264</v>
+        <v>7060565</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1527,9 +1507,19 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,22 +1534,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131086958</v>
+        <v>131085613</v>
       </c>
       <c r="B10" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,37 +1557,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585165</v>
+        <v>585222</v>
       </c>
       <c r="R10" t="n">
-        <v>7060565</v>
+        <v>7060481</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1626,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1636,7 +1631,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,22 +1651,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131087481</v>
+        <v>131085696</v>
       </c>
       <c r="B11" t="n">
-        <v>91836</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,33 +1674,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585150</v>
+        <v>585207</v>
       </c>
       <c r="R11" t="n">
-        <v>7060657</v>
+        <v>7060471</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1727,9 +1736,24 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1744,22 +1768,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131085696</v>
+        <v>131087481</v>
       </c>
       <c r="B12" t="n">
-        <v>57886</v>
+        <v>91837</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1767,42 +1791,33 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585207</v>
+        <v>585150</v>
       </c>
       <c r="R12" t="n">
-        <v>7060471</v>
+        <v>7060657</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1829,24 +1844,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,12 +1861,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1876,7 +1876,7 @@
         <v>131085209</v>
       </c>
       <c r="B13" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>131085114</v>
       </c>
       <c r="B14" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>131089847</v>
       </c>
       <c r="B15" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131092632</v>
+        <v>131085107</v>
       </c>
       <c r="B16" t="n">
-        <v>57886</v>
+        <v>91837</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2197,39 +2197,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585099</v>
+        <v>585194</v>
       </c>
       <c r="R16" t="n">
-        <v>7060260</v>
+        <v>7060227</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2262,11 +2253,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2293,10 +2279,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131085107</v>
+        <v>131092632</v>
       </c>
       <c r="B17" t="n">
-        <v>91836</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2304,30 +2290,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585194</v>
+        <v>585099</v>
       </c>
       <c r="R17" t="n">
-        <v>7060227</v>
+        <v>7060260</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2360,6 +2355,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2389,7 +2389,7 @@
         <v>131092554</v>
       </c>
       <c r="B18" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>131086957</v>
       </c>
       <c r="B19" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131085737</v>
+        <v>131092560</v>
       </c>
       <c r="B20" t="n">
-        <v>79248</v>
+        <v>91813</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,21 +2621,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2645,13 +2645,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585170</v>
+        <v>585129</v>
       </c>
       <c r="R20" t="n">
-        <v>7060469</v>
+        <v>7060254</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2705,22 +2705,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131085446</v>
+        <v>131085737</v>
       </c>
       <c r="B21" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2752,13 +2752,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585301</v>
+        <v>585170</v>
       </c>
       <c r="R21" t="n">
-        <v>7060488</v>
+        <v>7060469</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2812,22 +2812,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131092560</v>
+        <v>131085446</v>
       </c>
       <c r="B22" t="n">
-        <v>91812</v>
+        <v>79249</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,21 +2835,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585129</v>
+        <v>585301</v>
       </c>
       <c r="R22" t="n">
-        <v>7060254</v>
+        <v>7060488</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2934,7 +2934,7 @@
         <v>131085201</v>
       </c>
       <c r="B23" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>131089835</v>
       </c>
       <c r="B24" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>131085180</v>
       </c>
       <c r="B25" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>131087026</v>
       </c>
       <c r="B26" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>131085159</v>
       </c>
       <c r="B27" t="n">
-        <v>56458</v>
+        <v>56459</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>131085171</v>
       </c>
       <c r="B28" t="n">
-        <v>91812</v>
+        <v>91813</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>131085178</v>
       </c>
       <c r="B29" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>131085484</v>
       </c>
       <c r="B30" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>131085240</v>
       </c>
       <c r="B31" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3890,10 +3890,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131085126</v>
+        <v>131092585</v>
       </c>
       <c r="B32" t="n">
-        <v>57066</v>
+        <v>91813</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3901,39 +3901,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585219</v>
+        <v>585130</v>
       </c>
       <c r="R32" t="n">
-        <v>7060240</v>
+        <v>7060263</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3995,7 +3990,7 @@
         <v>131085569</v>
       </c>
       <c r="B33" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4092,7 +4087,7 @@
         <v>131087388</v>
       </c>
       <c r="B34" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4189,7 +4184,7 @@
         <v>131092590</v>
       </c>
       <c r="B35" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4293,10 +4288,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131092585</v>
+        <v>131085126</v>
       </c>
       <c r="B36" t="n">
-        <v>91812</v>
+        <v>57067</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4304,34 +4299,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>585130</v>
+        <v>585219</v>
       </c>
       <c r="R36" t="n">
-        <v>7060263</v>
+        <v>7060240</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>

--- a/artfynd/A 3222-2026 artfynd.xlsx
+++ b/artfynd/A 3222-2026 artfynd.xlsx
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131085696</v>
+        <v>131087481</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,42 +1674,33 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585207</v>
+        <v>585150</v>
       </c>
       <c r="R11" t="n">
-        <v>7060471</v>
+        <v>7060657</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1736,24 +1727,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,22 +1744,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131087481</v>
+        <v>131085696</v>
       </c>
       <c r="B12" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,33 +1767,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585150</v>
+        <v>585207</v>
       </c>
       <c r="R12" t="n">
-        <v>7060657</v>
+        <v>7060471</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1844,9 +1829,24 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,12 +1861,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131085171</v>
+        <v>131085178</v>
       </c>
       <c r="B28" t="n">
-        <v>91813</v>
+        <v>91837</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3477,23 +3477,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3501,13 +3497,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585222</v>
+        <v>585225</v>
       </c>
       <c r="R28" t="n">
-        <v>7060254</v>
+        <v>7060258</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3534,9 +3530,19 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3551,22 +3557,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131085178</v>
+        <v>131085240</v>
       </c>
       <c r="B29" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3574,30 +3580,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585225</v>
+        <v>585289</v>
       </c>
       <c r="R29" t="n">
-        <v>7060258</v>
+        <v>7060293</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3629,7 +3644,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3639,7 +3654,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3666,10 +3686,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131085484</v>
+        <v>131085171</v>
       </c>
       <c r="B30" t="n">
-        <v>57887</v>
+        <v>91813</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3677,39 +3697,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585303</v>
+        <v>585222</v>
       </c>
       <c r="R30" t="n">
-        <v>7060488</v>
+        <v>7060254</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3742,11 +3757,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3773,7 +3783,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131085240</v>
+        <v>131085484</v>
       </c>
       <c r="B31" t="n">
         <v>57887</v>
@@ -3813,13 +3823,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585289</v>
+        <v>585303</v>
       </c>
       <c r="R31" t="n">
-        <v>7060293</v>
+        <v>7060488</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3846,24 +3856,14 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3878,22 +3878,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131092585</v>
+        <v>131085569</v>
       </c>
       <c r="B32" t="n">
-        <v>91813</v>
+        <v>79249</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3901,21 +3901,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585130</v>
+        <v>585249</v>
       </c>
       <c r="R32" t="n">
-        <v>7060263</v>
+        <v>7060505</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3987,7 +3987,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131085569</v>
+        <v>131087388</v>
       </c>
       <c r="B33" t="n">
         <v>79249</v>
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>585249</v>
+        <v>585131</v>
       </c>
       <c r="R33" t="n">
-        <v>7060505</v>
+        <v>7060627</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131087388</v>
+        <v>131092590</v>
       </c>
       <c r="B34" t="n">
         <v>79249</v>
@@ -4119,13 +4119,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>585131</v>
+        <v>585145</v>
       </c>
       <c r="R34" t="n">
-        <v>7060627</v>
+        <v>7060230</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4152,9 +4152,19 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4169,22 +4179,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131092590</v>
+        <v>131085126</v>
       </c>
       <c r="B35" t="n">
-        <v>79249</v>
+        <v>57067</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4192,37 +4202,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>585145</v>
+        <v>585219</v>
       </c>
       <c r="R35" t="n">
-        <v>7060230</v>
+        <v>7060240</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4249,19 +4264,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4276,22 +4281,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131085126</v>
+        <v>131092585</v>
       </c>
       <c r="B36" t="n">
-        <v>57067</v>
+        <v>91813</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4299,39 +4304,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>585219</v>
+        <v>585130</v>
       </c>
       <c r="R36" t="n">
-        <v>7060240</v>
+        <v>7060263</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>

--- a/artfynd/A 3222-2026 artfynd.xlsx
+++ b/artfynd/A 3222-2026 artfynd.xlsx
@@ -2186,10 +2186,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131085107</v>
+        <v>131092632</v>
       </c>
       <c r="B16" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2197,30 +2197,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585194</v>
+        <v>585099</v>
       </c>
       <c r="R16" t="n">
-        <v>7060227</v>
+        <v>7060260</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2253,6 +2262,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2279,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131092632</v>
+        <v>131085107</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,39 +2304,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585099</v>
+        <v>585194</v>
       </c>
       <c r="R17" t="n">
-        <v>7060260</v>
+        <v>7060227</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2355,11 +2360,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2610,10 +2610,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131092560</v>
+        <v>131085737</v>
       </c>
       <c r="B20" t="n">
-        <v>91813</v>
+        <v>79249</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,21 +2621,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2645,13 +2645,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585129</v>
+        <v>585170</v>
       </c>
       <c r="R20" t="n">
-        <v>7060254</v>
+        <v>7060469</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2705,19 +2705,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131085737</v>
+        <v>131085446</v>
       </c>
       <c r="B21" t="n">
         <v>79249</v>
@@ -2752,13 +2752,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585170</v>
+        <v>585301</v>
       </c>
       <c r="R21" t="n">
-        <v>7060469</v>
+        <v>7060488</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2812,22 +2812,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131085446</v>
+        <v>131092560</v>
       </c>
       <c r="B22" t="n">
-        <v>79249</v>
+        <v>91813</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,21 +2835,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585301</v>
+        <v>585129</v>
       </c>
       <c r="R22" t="n">
-        <v>7060488</v>
+        <v>7060254</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3569,10 +3569,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131085240</v>
+        <v>131085171</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>91813</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3580,42 +3580,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585289</v>
+        <v>585222</v>
       </c>
       <c r="R29" t="n">
-        <v>7060293</v>
+        <v>7060254</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3642,24 +3637,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3674,22 +3654,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131085171</v>
+        <v>131085484</v>
       </c>
       <c r="B30" t="n">
-        <v>91813</v>
+        <v>57887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3697,34 +3677,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585222</v>
+        <v>585303</v>
       </c>
       <c r="R30" t="n">
-        <v>7060254</v>
+        <v>7060488</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3757,6 +3742,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3783,7 +3773,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131085484</v>
+        <v>131085240</v>
       </c>
       <c r="B31" t="n">
         <v>57887</v>
@@ -3823,13 +3813,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585303</v>
+        <v>585289</v>
       </c>
       <c r="R31" t="n">
-        <v>7060488</v>
+        <v>7060293</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3856,14 +3846,24 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Färska ringhack gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3878,22 +3878,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131085569</v>
+        <v>131085126</v>
       </c>
       <c r="B32" t="n">
-        <v>79249</v>
+        <v>57067</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3901,34 +3901,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585249</v>
+        <v>585219</v>
       </c>
       <c r="R32" t="n">
-        <v>7060505</v>
+        <v>7060240</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3987,7 +3992,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131087388</v>
+        <v>131085569</v>
       </c>
       <c r="B33" t="n">
         <v>79249</v>
@@ -4022,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>585131</v>
+        <v>585249</v>
       </c>
       <c r="R33" t="n">
-        <v>7060627</v>
+        <v>7060505</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4084,7 +4089,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131092590</v>
+        <v>131087388</v>
       </c>
       <c r="B34" t="n">
         <v>79249</v>
@@ -4119,13 +4124,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>585145</v>
+        <v>585131</v>
       </c>
       <c r="R34" t="n">
-        <v>7060230</v>
+        <v>7060627</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4152,19 +4157,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4179,22 +4174,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131085126</v>
+        <v>131092590</v>
       </c>
       <c r="B35" t="n">
-        <v>57067</v>
+        <v>79249</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4202,42 +4197,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>585219</v>
+        <v>585145</v>
       </c>
       <c r="R35" t="n">
-        <v>7060240</v>
+        <v>7060230</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4264,9 +4254,19 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4281,12 +4281,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>

--- a/artfynd/A 3222-2026 artfynd.xlsx
+++ b/artfynd/A 3222-2026 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131085805</v>
+        <v>131085613</v>
       </c>
       <c r="B7" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,37 +1246,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585215</v>
+        <v>585222</v>
       </c>
       <c r="R7" t="n">
-        <v>7060513</v>
+        <v>7060481</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1320,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,22 +1340,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131092646</v>
+        <v>131085805</v>
       </c>
       <c r="B8" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,13 +1387,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585082</v>
+        <v>585215</v>
       </c>
       <c r="R8" t="n">
-        <v>7060264</v>
+        <v>7060513</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1410,9 +1420,19 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,22 +1447,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131086958</v>
+        <v>131092646</v>
       </c>
       <c r="B9" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,13 +1494,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585165</v>
+        <v>585082</v>
       </c>
       <c r="R9" t="n">
-        <v>7060565</v>
+        <v>7060264</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1507,19 +1527,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,22 +1544,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131085613</v>
+        <v>131086958</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,42 +1567,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585222</v>
+        <v>585165</v>
       </c>
       <c r="R10" t="n">
-        <v>7060481</v>
+        <v>7060565</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1621,7 +1626,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1631,12 +1636,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:52</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack gran</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,12 +1651,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1666,7 +1666,7 @@
         <v>131087481</v>
       </c>
       <c r="B11" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>131085696</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         <v>131085209</v>
       </c>
       <c r="B13" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>131085114</v>
       </c>
       <c r="B14" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>131089847</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131092632</v>
+        <v>131085107</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>91838</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2197,39 +2197,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585099</v>
+        <v>585194</v>
       </c>
       <c r="R16" t="n">
-        <v>7060260</v>
+        <v>7060227</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2262,11 +2253,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2293,10 +2279,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131085107</v>
+        <v>131092632</v>
       </c>
       <c r="B17" t="n">
-        <v>91837</v>
+        <v>57888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2304,30 +2290,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585194</v>
+        <v>585099</v>
       </c>
       <c r="R17" t="n">
-        <v>7060227</v>
+        <v>7060260</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2360,6 +2355,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2389,7 +2389,7 @@
         <v>131092554</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131086957</v>
+        <v>131092560</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>91814</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2504,39 +2504,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585162</v>
+        <v>585129</v>
       </c>
       <c r="R19" t="n">
-        <v>7060573</v>
+        <v>7060254</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2568,7 +2563,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2578,12 +2573,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2610,10 +2600,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131085737</v>
+        <v>131086957</v>
       </c>
       <c r="B20" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,37 +2611,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585170</v>
+        <v>585162</v>
       </c>
       <c r="R20" t="n">
-        <v>7060469</v>
+        <v>7060573</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2680,7 +2675,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2690,7 +2685,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2705,22 +2705,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131085446</v>
+        <v>131085737</v>
       </c>
       <c r="B21" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2752,13 +2752,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585301</v>
+        <v>585170</v>
       </c>
       <c r="R21" t="n">
-        <v>7060488</v>
+        <v>7060469</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2812,22 +2812,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131092560</v>
+        <v>131085446</v>
       </c>
       <c r="B22" t="n">
-        <v>91813</v>
+        <v>79250</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,21 +2835,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585129</v>
+        <v>585301</v>
       </c>
       <c r="R22" t="n">
-        <v>7060254</v>
+        <v>7060488</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2934,7 +2934,7 @@
         <v>131085201</v>
       </c>
       <c r="B23" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>131089835</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>131085180</v>
       </c>
       <c r="B25" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>131087026</v>
       </c>
       <c r="B26" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>131085159</v>
       </c>
       <c r="B27" t="n">
-        <v>56459</v>
+        <v>56460</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131085178</v>
+        <v>131085171</v>
       </c>
       <c r="B28" t="n">
-        <v>91837</v>
+        <v>91814</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3477,19 +3477,23 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3497,13 +3501,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585225</v>
+        <v>585222</v>
       </c>
       <c r="R28" t="n">
-        <v>7060258</v>
+        <v>7060254</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3530,19 +3534,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3557,22 +3551,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131085171</v>
+        <v>131085178</v>
       </c>
       <c r="B29" t="n">
-        <v>91813</v>
+        <v>91838</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3580,23 +3574,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3604,13 +3594,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585222</v>
+        <v>585225</v>
       </c>
       <c r="R29" t="n">
-        <v>7060254</v>
+        <v>7060258</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3637,9 +3627,19 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3654,12 +3654,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3669,7 +3669,7 @@
         <v>131085484</v>
       </c>
       <c r="B30" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>131085240</v>
       </c>
       <c r="B31" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3890,10 +3890,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131085126</v>
+        <v>131092585</v>
       </c>
       <c r="B32" t="n">
-        <v>57067</v>
+        <v>91814</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3901,39 +3901,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585219</v>
+        <v>585130</v>
       </c>
       <c r="R32" t="n">
-        <v>7060240</v>
+        <v>7060263</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3995,7 +3990,7 @@
         <v>131085569</v>
       </c>
       <c r="B33" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4092,7 +4087,7 @@
         <v>131087388</v>
       </c>
       <c r="B34" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4189,7 +4184,7 @@
         <v>131092590</v>
       </c>
       <c r="B35" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4293,10 +4288,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131092585</v>
+        <v>131085126</v>
       </c>
       <c r="B36" t="n">
-        <v>91813</v>
+        <v>57067</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4304,34 +4299,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>585130</v>
+        <v>585219</v>
       </c>
       <c r="R36" t="n">
-        <v>7060263</v>
+        <v>7060240</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>

--- a/artfynd/A 3222-2026 artfynd.xlsx
+++ b/artfynd/A 3222-2026 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131085613</v>
+        <v>131085805</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,42 +1246,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585222</v>
+        <v>585215</v>
       </c>
       <c r="R7" t="n">
-        <v>7060481</v>
+        <v>7060513</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,12 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:52</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack gran</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,19 +1330,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131085805</v>
+        <v>131092646</v>
       </c>
       <c r="B8" t="n">
         <v>79250</v>
@@ -1387,13 +1377,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585215</v>
+        <v>585082</v>
       </c>
       <c r="R8" t="n">
-        <v>7060513</v>
+        <v>7060264</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,19 +1410,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,19 +1427,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131092646</v>
+        <v>131086958</v>
       </c>
       <c r="B9" t="n">
         <v>79250</v>
@@ -1494,13 +1474,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585082</v>
+        <v>585165</v>
       </c>
       <c r="R9" t="n">
-        <v>7060264</v>
+        <v>7060565</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1527,9 +1507,19 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,22 +1534,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131086958</v>
+        <v>131085613</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,37 +1557,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585165</v>
+        <v>585222</v>
       </c>
       <c r="R10" t="n">
-        <v>7060565</v>
+        <v>7060481</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1626,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1636,7 +1631,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,12 +1651,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131085107</v>
+        <v>131092632</v>
       </c>
       <c r="B16" t="n">
-        <v>91838</v>
+        <v>57888</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2197,30 +2197,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585194</v>
+        <v>585099</v>
       </c>
       <c r="R16" t="n">
-        <v>7060227</v>
+        <v>7060260</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2253,6 +2262,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2279,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131092632</v>
+        <v>131085107</v>
       </c>
       <c r="B17" t="n">
-        <v>57888</v>
+        <v>91838</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,39 +2304,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585099</v>
+        <v>585194</v>
       </c>
       <c r="R17" t="n">
-        <v>7060260</v>
+        <v>7060227</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2355,11 +2360,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2386,7 +2386,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131092554</v>
+        <v>131086957</v>
       </c>
       <c r="B18" t="n">
         <v>57888</v>
@@ -2417,7 +2417,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2426,13 +2426,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585147</v>
+        <v>585162</v>
       </c>
       <c r="R18" t="n">
-        <v>7060312</v>
+        <v>7060573</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2459,14 +2459,24 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre ringhack, gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2481,22 +2491,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131092560</v>
+        <v>131085737</v>
       </c>
       <c r="B19" t="n">
-        <v>91814</v>
+        <v>79250</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2504,21 +2514,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2528,13 +2538,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585129</v>
+        <v>585170</v>
       </c>
       <c r="R19" t="n">
-        <v>7060254</v>
+        <v>7060469</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2563,7 +2573,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2573,7 +2583,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2588,22 +2598,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131086957</v>
+        <v>131085446</v>
       </c>
       <c r="B20" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2611,39 +2621,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585162</v>
+        <v>585301</v>
       </c>
       <c r="R20" t="n">
-        <v>7060573</v>
+        <v>7060488</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2675,7 +2680,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2685,12 +2690,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2717,10 +2717,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131085737</v>
+        <v>131092560</v>
       </c>
       <c r="B21" t="n">
-        <v>79250</v>
+        <v>91814</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,21 +2728,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2752,13 +2752,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585170</v>
+        <v>585129</v>
       </c>
       <c r="R21" t="n">
-        <v>7060469</v>
+        <v>7060254</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2812,22 +2812,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131085446</v>
+        <v>131092554</v>
       </c>
       <c r="B22" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,37 +2835,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585301</v>
+        <v>585147</v>
       </c>
       <c r="R22" t="n">
-        <v>7060488</v>
+        <v>7060312</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2892,19 +2897,14 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:41</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2919,12 +2919,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131085171</v>
+        <v>131085178</v>
       </c>
       <c r="B28" t="n">
-        <v>91814</v>
+        <v>91838</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3477,23 +3477,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3501,13 +3497,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585222</v>
+        <v>585225</v>
       </c>
       <c r="R28" t="n">
-        <v>7060254</v>
+        <v>7060258</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3534,9 +3530,19 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3551,22 +3557,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131085178</v>
+        <v>131085171</v>
       </c>
       <c r="B29" t="n">
-        <v>91838</v>
+        <v>91814</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3574,19 +3580,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3594,13 +3604,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585225</v>
+        <v>585222</v>
       </c>
       <c r="R29" t="n">
-        <v>7060258</v>
+        <v>7060254</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3627,19 +3637,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3654,12 +3654,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3890,10 +3890,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131092585</v>
+        <v>131085569</v>
       </c>
       <c r="B32" t="n">
-        <v>91814</v>
+        <v>79250</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3901,21 +3901,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585130</v>
+        <v>585249</v>
       </c>
       <c r="R32" t="n">
-        <v>7060263</v>
+        <v>7060505</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3987,7 +3987,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131085569</v>
+        <v>131087388</v>
       </c>
       <c r="B33" t="n">
         <v>79250</v>
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>585249</v>
+        <v>585131</v>
       </c>
       <c r="R33" t="n">
-        <v>7060505</v>
+        <v>7060627</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131087388</v>
+        <v>131092590</v>
       </c>
       <c r="B34" t="n">
         <v>79250</v>
@@ -4119,13 +4119,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>585131</v>
+        <v>585145</v>
       </c>
       <c r="R34" t="n">
-        <v>7060627</v>
+        <v>7060230</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4152,9 +4152,19 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4169,22 +4179,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131092590</v>
+        <v>131092585</v>
       </c>
       <c r="B35" t="n">
-        <v>79250</v>
+        <v>91814</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4192,21 +4202,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4216,13 +4226,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>585145</v>
+        <v>585130</v>
       </c>
       <c r="R35" t="n">
-        <v>7060230</v>
+        <v>7060263</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4249,19 +4259,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4276,12 +4276,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>

--- a/artfynd/A 3222-2026 artfynd.xlsx
+++ b/artfynd/A 3222-2026 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131085805</v>
+        <v>131085613</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,37 +1246,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585215</v>
+        <v>585222</v>
       </c>
       <c r="R7" t="n">
-        <v>7060513</v>
+        <v>7060481</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1320,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,22 +1340,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131092646</v>
+        <v>131085805</v>
       </c>
       <c r="B8" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,13 +1387,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585082</v>
+        <v>585215</v>
       </c>
       <c r="R8" t="n">
-        <v>7060264</v>
+        <v>7060513</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1410,9 +1420,19 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,22 +1447,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131086958</v>
+        <v>131092646</v>
       </c>
       <c r="B9" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,13 +1494,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585165</v>
+        <v>585082</v>
       </c>
       <c r="R9" t="n">
-        <v>7060565</v>
+        <v>7060264</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1507,19 +1527,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,22 +1544,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131085613</v>
+        <v>131086958</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,42 +1567,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585222</v>
+        <v>585165</v>
       </c>
       <c r="R10" t="n">
-        <v>7060481</v>
+        <v>7060565</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1621,7 +1626,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1631,12 +1636,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:52</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack gran</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,12 +1651,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1666,7 +1666,7 @@
         <v>131087481</v>
       </c>
       <c r="B11" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>131085696</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         <v>131085209</v>
       </c>
       <c r="B13" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>131085114</v>
       </c>
       <c r="B14" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>131089847</v>
       </c>
       <c r="B15" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131092632</v>
+        <v>131085107</v>
       </c>
       <c r="B16" t="n">
-        <v>57888</v>
+        <v>91841</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2197,39 +2197,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585099</v>
+        <v>585194</v>
       </c>
       <c r="R16" t="n">
-        <v>7060260</v>
+        <v>7060227</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2262,11 +2253,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2293,10 +2279,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131085107</v>
+        <v>131092632</v>
       </c>
       <c r="B17" t="n">
-        <v>91838</v>
+        <v>57891</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2304,30 +2290,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585194</v>
+        <v>585099</v>
       </c>
       <c r="R17" t="n">
-        <v>7060227</v>
+        <v>7060260</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2360,6 +2355,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2386,10 +2386,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131086957</v>
+        <v>131085737</v>
       </c>
       <c r="B18" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,42 +2397,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585162</v>
+        <v>585170</v>
       </c>
       <c r="R18" t="n">
-        <v>7060573</v>
+        <v>7060469</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2461,7 +2456,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2471,12 +2466,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2491,22 +2481,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131085737</v>
+        <v>131085446</v>
       </c>
       <c r="B19" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2538,13 +2528,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585170</v>
+        <v>585301</v>
       </c>
       <c r="R19" t="n">
-        <v>7060469</v>
+        <v>7060488</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2573,7 +2563,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2583,7 +2573,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2598,22 +2588,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131085446</v>
+        <v>131092560</v>
       </c>
       <c r="B20" t="n">
-        <v>79250</v>
+        <v>91817</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,21 +2611,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2645,10 +2635,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585301</v>
+        <v>585129</v>
       </c>
       <c r="R20" t="n">
-        <v>7060488</v>
+        <v>7060254</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2680,7 +2670,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2690,7 +2680,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2717,10 +2707,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131092560</v>
+        <v>131092554</v>
       </c>
       <c r="B21" t="n">
-        <v>91814</v>
+        <v>57891</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,37 +2718,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585129</v>
+        <v>585147</v>
       </c>
       <c r="R21" t="n">
-        <v>7060254</v>
+        <v>7060312</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2785,19 +2780,14 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:17</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2812,22 +2802,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131092554</v>
+        <v>131086957</v>
       </c>
       <c r="B22" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2855,7 +2845,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2864,13 +2854,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585147</v>
+        <v>585162</v>
       </c>
       <c r="R22" t="n">
-        <v>7060312</v>
+        <v>7060573</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2897,14 +2887,24 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Äldre ringhack, gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2919,12 +2919,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2934,7 +2934,7 @@
         <v>131085201</v>
       </c>
       <c r="B23" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>131089835</v>
       </c>
       <c r="B24" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>131085180</v>
       </c>
       <c r="B25" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>131087026</v>
       </c>
       <c r="B26" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>131085159</v>
       </c>
       <c r="B27" t="n">
-        <v>56460</v>
+        <v>56463</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131085178</v>
+        <v>131085171</v>
       </c>
       <c r="B28" t="n">
-        <v>91838</v>
+        <v>91817</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3477,19 +3477,23 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3497,13 +3501,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585225</v>
+        <v>585222</v>
       </c>
       <c r="R28" t="n">
-        <v>7060258</v>
+        <v>7060254</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3530,19 +3534,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3557,22 +3551,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131085171</v>
+        <v>131085178</v>
       </c>
       <c r="B29" t="n">
-        <v>91814</v>
+        <v>91841</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3580,23 +3574,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3604,13 +3594,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585222</v>
+        <v>585225</v>
       </c>
       <c r="R29" t="n">
-        <v>7060254</v>
+        <v>7060258</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3637,9 +3627,19 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3654,12 +3654,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3669,7 +3669,7 @@
         <v>131085484</v>
       </c>
       <c r="B30" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>131085240</v>
       </c>
       <c r="B31" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>131085569</v>
       </c>
       <c r="B32" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3987,10 +3987,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131087388</v>
+        <v>131092585</v>
       </c>
       <c r="B33" t="n">
-        <v>79250</v>
+        <v>91817</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3998,21 +3998,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>585131</v>
+        <v>585130</v>
       </c>
       <c r="R33" t="n">
-        <v>7060627</v>
+        <v>7060263</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4084,10 +4084,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131092590</v>
+        <v>131087388</v>
       </c>
       <c r="B34" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4119,13 +4119,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>585145</v>
+        <v>585131</v>
       </c>
       <c r="R34" t="n">
-        <v>7060230</v>
+        <v>7060627</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4152,19 +4152,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4179,22 +4169,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131092585</v>
+        <v>131092590</v>
       </c>
       <c r="B35" t="n">
-        <v>91814</v>
+        <v>79253</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4202,21 +4192,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4226,13 +4216,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>585130</v>
+        <v>585145</v>
       </c>
       <c r="R35" t="n">
-        <v>7060263</v>
+        <v>7060230</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4259,9 +4249,19 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4276,12 +4276,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4291,7 +4291,7 @@
         <v>131085126</v>
       </c>
       <c r="B36" t="n">
-        <v>57067</v>
+        <v>57070</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 3222-2026 artfynd.xlsx
+++ b/artfynd/A 3222-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115227715</v>
+        <v>131085171</v>
       </c>
       <c r="B2" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585131</v>
+        <v>585222</v>
       </c>
       <c r="R2" t="n">
-        <v>7060271</v>
+        <v>7060254</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:05</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:05</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115228120</v>
+        <v>131092560</v>
       </c>
       <c r="B3" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585055</v>
+        <v>585129</v>
       </c>
       <c r="R3" t="n">
-        <v>7060338</v>
+        <v>7060254</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115227814</v>
+        <v>131092585</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,42 +890,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585123</v>
+        <v>585130</v>
       </c>
       <c r="R4" t="n">
-        <v>7060247</v>
+        <v>7060263</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,22 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,70 +964,64 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115227996</v>
+        <v>126270731</v>
       </c>
       <c r="B5" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585146</v>
+        <v>585127</v>
       </c>
       <c r="R5" t="n">
-        <v>7060285</v>
+        <v>7060624</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,22 +1045,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:12</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:12</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,70 +1059,67 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Maria Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126270731</v>
+        <v>131085180</v>
       </c>
       <c r="B6" t="n">
-        <v>100516</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1365</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Timmeråsen, Ång</t>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585127</v>
+        <v>585223</v>
       </c>
       <c r="R6" t="n">
-        <v>7060624</v>
+        <v>7060252</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,12 +1143,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1216,72 +1157,66 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131085613</v>
+        <v>131085201</v>
       </c>
       <c r="B7" t="n">
-        <v>57891</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585222</v>
+        <v>585260</v>
       </c>
       <c r="R7" t="n">
-        <v>7060481</v>
+        <v>7060264</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1245,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,12 +1255,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:52</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack gran</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,26 +1270,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131085805</v>
+        <v>131085446</v>
       </c>
       <c r="B8" t="n">
-        <v>79253</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1387,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585215</v>
+        <v>585301</v>
       </c>
       <c r="R8" t="n">
-        <v>7060513</v>
+        <v>7060488</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1352,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1362,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,14 +1389,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131092646</v>
+        <v>131085569</v>
       </c>
       <c r="B9" t="n">
-        <v>79253</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1494,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585082</v>
+        <v>585249</v>
       </c>
       <c r="R9" t="n">
-        <v>7060264</v>
+        <v>7060505</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1556,14 +1486,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131086958</v>
+        <v>131085737</v>
       </c>
       <c r="B10" t="n">
-        <v>79253</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1591,13 +1521,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585165</v>
+        <v>585170</v>
       </c>
       <c r="R10" t="n">
-        <v>7060565</v>
+        <v>7060469</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1626,7 +1556,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1636,7 +1566,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,42 +1581,46 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131087481</v>
+        <v>131085805</v>
       </c>
       <c r="B11" t="n">
-        <v>91841</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1694,13 +1628,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585150</v>
+        <v>585215</v>
       </c>
       <c r="R11" t="n">
-        <v>7060657</v>
+        <v>7060513</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1727,9 +1661,19 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1744,62 +1688,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131085696</v>
+        <v>131086958</v>
       </c>
       <c r="B12" t="n">
-        <v>57891</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585207</v>
+        <v>585165</v>
       </c>
       <c r="R12" t="n">
-        <v>7060471</v>
+        <v>7060565</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,7 +1770,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1841,12 +1780,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1873,30 +1807,34 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131085209</v>
+        <v>131087388</v>
       </c>
       <c r="B13" t="n">
-        <v>91841</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1904,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585267</v>
+        <v>585131</v>
       </c>
       <c r="R13" t="n">
-        <v>7060286</v>
+        <v>7060627</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1937,19 +1875,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,42 +1892,46 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131085114</v>
+        <v>131092590</v>
       </c>
       <c r="B14" t="n">
-        <v>91841</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2007,13 +1939,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585200</v>
+        <v>585145</v>
       </c>
       <c r="R14" t="n">
-        <v>7060231</v>
+        <v>7060230</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2040,9 +1972,19 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2057,62 +1999,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131089847</v>
+        <v>131092646</v>
       </c>
       <c r="B15" t="n">
-        <v>57891</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585024</v>
+        <v>585082</v>
       </c>
       <c r="R15" t="n">
-        <v>7060313</v>
+        <v>7060264</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2142,24 +2079,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2186,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131085107</v>
+        <v>115227814</v>
       </c>
       <c r="B16" t="n">
-        <v>91841</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2197,33 +2119,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585194</v>
+        <v>585123</v>
       </c>
       <c r="R16" t="n">
-        <v>7060227</v>
+        <v>7060247</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2247,12 +2178,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2267,22 +2208,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131092632</v>
+        <v>115227996</v>
       </c>
       <c r="B17" t="n">
-        <v>57891</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2310,7 +2251,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2319,13 +2260,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585099</v>
+        <v>585146</v>
       </c>
       <c r="R17" t="n">
-        <v>7060260</v>
+        <v>7060285</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2349,17 +2290,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2374,22 +2320,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131085737</v>
+        <v>118395387</v>
       </c>
       <c r="B18" t="n">
-        <v>79253</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,37 +2343,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+          <t>Timmeråsen, Timmeråsen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585170</v>
+        <v>585100</v>
       </c>
       <c r="R18" t="n">
-        <v>7060469</v>
+        <v>7060200</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2451,22 +2402,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2481,22 +2432,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131085446</v>
+        <v>131085086</v>
       </c>
       <c r="B19" t="n">
-        <v>79253</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2504,37 +2455,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585301</v>
+        <v>585166</v>
       </c>
       <c r="R19" t="n">
-        <v>7060488</v>
+        <v>7060188</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2561,19 +2517,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2588,22 +2534,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131092560</v>
+        <v>131085240</v>
       </c>
       <c r="B20" t="n">
-        <v>91817</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2611,34 +2557,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585129</v>
+        <v>585289</v>
       </c>
       <c r="R20" t="n">
-        <v>7060254</v>
+        <v>7060293</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2670,7 +2621,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2680,7 +2631,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2707,10 +2663,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131092554</v>
+        <v>131085484</v>
       </c>
       <c r="B21" t="n">
-        <v>57891</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,7 +2694,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2747,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585147</v>
+        <v>585303</v>
       </c>
       <c r="R21" t="n">
-        <v>7060312</v>
+        <v>7060488</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2787,7 +2743,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre ringhack, gran</t>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2814,10 +2770,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131086957</v>
+        <v>131085613</v>
       </c>
       <c r="B22" t="n">
-        <v>57891</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,13 +2810,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585162</v>
+        <v>585222</v>
       </c>
       <c r="R22" t="n">
-        <v>7060573</v>
+        <v>7060481</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2889,7 +2845,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2899,12 +2855,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2919,22 +2875,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131085201</v>
+        <v>131085696</v>
       </c>
       <c r="B23" t="n">
-        <v>79253</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2942,34 +2898,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585260</v>
+        <v>585207</v>
       </c>
       <c r="R23" t="n">
-        <v>7060264</v>
+        <v>7060471</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,7 +2962,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3011,7 +2972,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3038,10 +3004,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131089835</v>
+        <v>131086957</v>
       </c>
       <c r="B24" t="n">
-        <v>57891</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3078,13 +3044,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585046</v>
+        <v>585162</v>
       </c>
       <c r="R24" t="n">
-        <v>7060333</v>
+        <v>7060573</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3113,7 +3079,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3123,12 +3089,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska ringhack gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3143,22 +3109,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131085180</v>
+        <v>131089835</v>
       </c>
       <c r="B25" t="n">
-        <v>79253</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3166,34 +3132,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585223</v>
+        <v>585046</v>
       </c>
       <c r="R25" t="n">
-        <v>7060252</v>
+        <v>7060333</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3223,9 +3194,24 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3252,10 +3238,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131087026</v>
+        <v>131089847</v>
       </c>
       <c r="B26" t="n">
-        <v>58050</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3263,27 +3249,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3292,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585192</v>
+        <v>585024</v>
       </c>
       <c r="R26" t="n">
-        <v>7060563</v>
+        <v>7060313</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3327,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3337,7 +3323,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3364,10 +3355,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131085159</v>
+        <v>131092554</v>
       </c>
       <c r="B27" t="n">
-        <v>56463</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3375,27 +3366,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3404,10 +3395,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585222</v>
+        <v>585147</v>
       </c>
       <c r="R27" t="n">
-        <v>7060247</v>
+        <v>7060312</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3440,6 +3431,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3466,10 +3462,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131085171</v>
+        <v>131092632</v>
       </c>
       <c r="B28" t="n">
-        <v>91817</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3477,34 +3473,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585222</v>
+        <v>585099</v>
       </c>
       <c r="R28" t="n">
-        <v>7060254</v>
+        <v>7060260</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3537,6 +3538,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3563,44 +3569,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131085178</v>
+        <v>131085126</v>
       </c>
       <c r="B29" t="n">
-        <v>91841</v>
+        <v>57132</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585225</v>
+        <v>585219</v>
       </c>
       <c r="R29" t="n">
-        <v>7060258</v>
+        <v>7060240</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3627,19 +3642,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3654,22 +3659,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131085484</v>
+        <v>131087026</v>
       </c>
       <c r="B30" t="n">
-        <v>57891</v>
+        <v>58114</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3677,27 +3682,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3706,10 +3711,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585303</v>
+        <v>585192</v>
       </c>
       <c r="R30" t="n">
-        <v>7060488</v>
+        <v>7060563</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3739,14 +3744,19 @@
           <t>2026-02-09</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack gran</t>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3773,10 +3783,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131085240</v>
+        <v>131085159</v>
       </c>
       <c r="B31" t="n">
-        <v>57891</v>
+        <v>56522</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3784,21 +3794,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3813,13 +3823,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585289</v>
+        <v>585222</v>
       </c>
       <c r="R31" t="n">
-        <v>7060293</v>
+        <v>7060247</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3846,24 +3856,9 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3878,515 +3873,15 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>131085569</v>
-      </c>
-      <c r="B32" t="n">
-        <v>79253</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>585249</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7060505</v>
-      </c>
-      <c r="S32" t="n">
-        <v>15</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>131092585</v>
-      </c>
-      <c r="B33" t="n">
-        <v>91817</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>585130</v>
-      </c>
-      <c r="R33" t="n">
-        <v>7060263</v>
-      </c>
-      <c r="S33" t="n">
-        <v>15</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>131087388</v>
-      </c>
-      <c r="B34" t="n">
-        <v>79253</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>585131</v>
-      </c>
-      <c r="R34" t="n">
-        <v>7060627</v>
-      </c>
-      <c r="S34" t="n">
-        <v>15</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>131092590</v>
-      </c>
-      <c r="B35" t="n">
-        <v>79253</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>585145</v>
-      </c>
-      <c r="R35" t="n">
-        <v>7060230</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>131085126</v>
-      </c>
-      <c r="B36" t="n">
-        <v>57070</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>102612</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Järpe</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>585219</v>
-      </c>
-      <c r="R36" t="n">
-        <v>7060240</v>
-      </c>
-      <c r="S36" t="n">
-        <v>15</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3222-2026 artfynd.xlsx
+++ b/artfynd/A 3222-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131085171</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131092560</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131092585</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126270731</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131085180</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131085201</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131085446</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131085569</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131085737</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1697,6 +1747,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131085805</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1804,6 +1859,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131086958</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1901,6 +1961,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131087388</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2008,6 +2073,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131092590</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2105,6 +2175,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131092646</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2217,6 +2292,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115227814</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2329,6 +2409,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115227996</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2441,6 +2526,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118395387</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2543,6 +2633,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131085086</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2660,6 +2755,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131085240</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2767,6 +2867,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131085484</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2884,6 +2989,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131085613</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3001,6 +3111,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131085696</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3118,6 +3233,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131086957</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3235,6 +3355,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131089835</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3352,6 +3477,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131089847</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3459,6 +3589,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131092554</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3566,6 +3701,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131092632</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3668,6 +3808,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131085126</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3780,6 +3925,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131087026</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3882,8 +4032,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131085159</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>